--- a/ig/DM-OCTOBRE-2026/ValueSet-JDV-J62-PracticeSettingCode-DMP.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-JDV-J62-PracticeSettingCode-DMP.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="56">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20230922120000</t>
+    <t>20261102120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-22T12:00:00+01:00</t>
+    <t>2026-11-02T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -173,6 +173,12 @@
   </si>
   <si>
     <t>SAMU/SMUR</t>
+  </si>
+  <si>
+    <t>ESSMS</t>
+  </si>
+  <si>
+    <t>Etablissement ou Service Social ou Médico-Social</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_A01-CadreExercice/FHIR/TRE-A01-CadreExercice</t>
@@ -491,7 +497,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -580,18 +586,26 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>32</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
         <v>33</v>
       </c>
-      <c r="B12" t="s" s="2">
-        <v>53</v>
+      <c r="B13" t="s" s="2">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
